--- a/old_send/db/new_df.xlsx
+++ b/old_send/db/new_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,96 +457,92 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>1900</v>
+        <v>1678</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2701806564001010180</t>
+          <t>2701817257048022364</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-03-31 23:28:12</t>
+          <t>2026-04-03 23:20:08</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1903</v>
+        <v>1681</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4502247337001013318</t>
+          <t>2701817040044003098</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-03-31 23:07:17</t>
+          <t>2026-04-03 23:14:41</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>加赠岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1905</v>
+        <v>1683</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4502235601011032030</t>
+          <t>2701823233033033583</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-03-31 22:58:41</t>
+          <t>2026-04-03 23:04:55</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>加赠金香鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>清香桂花</t>
+          <t>浓香芝兰</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>1909</v>
+        <v>1686</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4502240426001039235</t>
+          <t>4502256697040025642</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-03-31 22:39:23</t>
+          <t>2026-04-03 23:01:13</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -554,127 +550,139 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+          <t>加赠庄园蜜兰7g*1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>1912</v>
+        <v>1688</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2701797243198020465</t>
+          <t>4502249895042005807</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-03-31 22:33:09</t>
+          <t>2026-04-03 22:52:55</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>1914</v>
+        <v>1691</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2701791518183016163</t>
+          <t>4502255186035111709</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-03-31 21:28:41</t>
+          <t>2026-04-03 21:27:10</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>加赠清香桂花7g*1</t>
+          <t>加赠庄园蜜兰7g*1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>1916</v>
+        <v>1694</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2701794542201032066</t>
+          <t>2701819634037001090</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-03-31 21:27:29</t>
+          <t>2026-04-03 20:13:20</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>1918</v>
+        <v>1697</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4502237293002011335</t>
+          <t>4502250648033004314</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-03-31 21:08:02</t>
+          <t>2026-04-03 19:37:45</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>1920</v>
+        <v>1699</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2701804839001105273</t>
+          <t>2701813692032032489</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-03-31 20:40:51</t>
+          <t>2026-04-03 18:44:46</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -682,55 +690,51 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1加赠 庄园锯朵仔7g*1</t>
+          <t>加赠老丛私房杏仁50g*1加赠：六大香型组合品鉴装7g*6</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>老丛私房宋种</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>1923</v>
+        <v>1703</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2701795803198009082</t>
+          <t>2701814052033093676</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-03-31 20:28:59</t>
+          <t>2026-04-03 18:22:58</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1加赠 庄园锯朵仔7g*1</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>1926</v>
+        <v>1705</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4502222856174082946</t>
+          <t>4502256516032025136</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-03-31 20:04:42</t>
+          <t>2026-04-03 18:14:44</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -739,46 +743,50 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>1928</v>
+        <v>1707</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4502231029177043415</t>
+          <t>2701819202024010588</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-03-31 19:52:33</t>
+          <t>2026-04-03 17:22:33</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>加赠 庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>1930</v>
+        <v>1709</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2701791698170013497</t>
+          <t>2701821180014200751</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-03-31 19:49:15</t>
+          <t>2026-04-03 17:04:33</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -787,22 +795,22 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>1932</v>
+        <v>1711</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2701789968180015555</t>
+          <t>2701810668035000563</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-03-31 19:46:19</t>
+          <t>2026-04-03 16:42:58</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -811,74 +819,74 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>1934</v>
+        <v>1713</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4502236214005003209</t>
+          <t>2701814628021026984</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-03-31 19:32:27</t>
+          <t>2026-04-03 16:02:22</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>加赠老丛私房杏仁50g*1加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>金香鸭屎+庄园蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>1938</v>
+        <v>1715</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4502220447159030037</t>
+          <t>2701821255022049886</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-03-31 19:24:14</t>
+          <t>2026-04-03 16:01:55</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>面值:面值F</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>1939</v>
+        <v>1717</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4502220267155015834</t>
+          <t>2701818012018002465</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-03-31 19:08:25</t>
+          <t>2026-04-03 15:58:27</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -887,46 +895,50 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>1942</v>
+        <v>1719</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4502218248180019946</t>
+          <t>2701828273019015281</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-03-31 18:03:23</t>
+          <t>2026-04-03 15:01:02</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>加赠 羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园东方红</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>1945</v>
+        <v>1722</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4502225019144020841</t>
+          <t>2701824277019015281</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-03-31 16:56:00</t>
+          <t>2026-04-03 15:00:31</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -935,22 +947,22 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>面值:面值B</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>1947</v>
+        <v>1723</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4502220411171023639</t>
+          <t>2701820426019015281</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-03-31 16:30:05</t>
+          <t>2026-04-03 14:47:43</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -959,74 +971,74 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>庄园东方红</t>
+          <t>面值:面值B</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>1949</v>
+        <v>1724</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2701792491184017692</t>
+          <t>2701820173016015398</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-03-31 16:29:20</t>
+          <t>2026-04-03 13:27:45</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>老丛私房姜花香</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>1951</v>
+        <v>1727</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2701787304190017692</t>
+          <t>2701816032017002281</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-03-31 16:28:47</t>
+          <t>2026-04-03 13:03:46</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>加赠老丛私房杏仁50g*2</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>老丛私房宋种</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>1953</v>
+        <v>1730</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2701791805182002151</t>
+          <t>2701812756017022880</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-03-31 16:17:12</t>
+          <t>2026-04-03 12:45:10</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1034,55 +1046,51 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+          <t>加赠 羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>1956</v>
+        <v>1734</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2701791194162001761</t>
+          <t>2701815746018013698</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-03-31 15:13:34</t>
+          <t>2026-04-03 12:44:16</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>加赠 岽顶蜜兰香7g*1  清香桂花7g*1</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>面值:面值B</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>1959</v>
+        <v>1735</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4502214795157034930</t>
+          <t>4502253279010009532</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-03-31 15:10:02</t>
+          <t>2026-04-03 11:14:48</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1091,32 +1099,28 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>1961</v>
+        <v>1737</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2701791015166049487</t>
+          <t>4502260009010018343</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-03-31 14:54:13</t>
+          <t>2026-04-03 09:49:56</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>加赠老丛私房杏仁50g*1，老丛私房鸭屎7g*1</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -1125,16 +1129,16 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>1964</v>
+        <v>1739</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2701799725170012660</t>
+          <t>4502261774006027525</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-03-31 14:50:42</t>
+          <t>2026-04-03 09:27:19</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1143,599 +1147,2878 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>十年陈窖藏鸭屎香</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
+        <v>1740</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2701818339011065378</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-04-03 09:12:07</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>加赠 羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>1742</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>4502260911009018511</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-04-03 09:02:38</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>1744</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2701818840002160972</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-04-02 23:58:29</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>发顺丰
+加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>1746</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4502250471005011534</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-04-02 23:21:03</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>1748</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2701825501001081494</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-04-02 23:00:37</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4502252916004055819</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-04-02 22:36:52</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>加赠 清香桂花7g*1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>1752</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>4502250468003018638</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-04-02 22:33:29</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>1755</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2701814880001035591</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-04-02 21:55:52</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>加赠 金香鸭屎7g*1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>六大香型进阶版</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>1757</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2701806098060034154</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-04-02 21:22:34</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>100</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>1760</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2701810095056002766</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-04-02 21:05:29</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>加赠 羊脂玉茶具（含公道杯）*1
+加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>1763</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2701818339001023966</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-04-02 21:01:08</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>1765</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2701803576061003299</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-04-02 19:56:40</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>1767</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>4502234016066001015</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-04-02 19:55:35</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>100</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">加赠 庄园锯朵仔7g*1 </t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>4502241936054016738</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-04-02 19:54:48</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>1771</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2701807287055004952</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-04-02 19:50:03</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>100</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>1774</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2701804046053006778</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:56:16</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>1778</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2701808509064016097</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:28:36</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>1780</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2701813729044003291</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:24:46</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>100</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>1783</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>4502230560053073218</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:22:10</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>1785</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2701800050059107679</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:20:18</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>1788</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>4502246330043009249</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:50:58</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>100</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>1792</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2701808364042003875</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-04-02 12:24:27</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>1794</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2701805595046007580</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-04-02 12:17:42</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>1796</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>4502238806040006934</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-04-02 11:57:08</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1 
+加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>老丛私房宋种</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>1798</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>4502242044046003233</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:26:55</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>加赠岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>1800</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2701798106041008064</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:14:37</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>悠山蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>1802</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2701808220041044550</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:40:16</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>1804</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>4502250614034042532</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:28:40</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>加赠 羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>1807</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2701806420037025585</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-04-02 06:51:43</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>1811</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2701799186038011567</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-04-02 01:39:24</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>加赠 羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>庄园锯朵仔</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>1821</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>4502240965033042424</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-04-02 00:11:30</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>1824</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2701805595034018181</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-04-02 00:04:24</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>老丛私房东方红</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>1826</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2701806530030004351</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-04-01 23:42:08</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>1829</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2701814737029004351</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-04-01 23:40:01</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>1832</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2701805846029027452</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:38:48</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>浓香芝兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>1834</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>4502248993028007324</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:27:53</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>1838</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2701814305038024189</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:26:12</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>100</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>1840</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2701808364026151582</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:58:02</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>1844</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2701799904037027895</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:21:55</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>1846</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2701809697036040089</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:20:01</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>1849</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>4502238300028004836</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:44:42</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>1852</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2701804404026005099</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:29:33</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>1854</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2701809517026026997</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:29:12</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2.0高阶版</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>1855</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2701809697025042186</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:55:11</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>1857</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>4502249929020017638</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:37:53</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>1860</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>4502236971023001620</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:28:06</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>1863</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>4502235312017002414</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:13:03</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>1866</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>4502237007013001606</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:45:21</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>100</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>1868</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>4502245897014044513</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:27:36</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>加赠：六大组合品鉴装42g*1</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>四大老丛</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>1870</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>4502242297013019309</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:24:30</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>1872</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>4502246834011026149</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:18:09</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>面值:面值C</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>1873</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>4502237040010009533</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:03:53</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*2加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>十年陈窖藏鸭屎香</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>1878</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2701803900011083391</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:44:59</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>九大香型</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>1880</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>4502237832016008438</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:16:16</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>老丛私房鸭屎香</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>1882</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2701798898025035993</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:12:02</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>1885</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>4502239488007028120</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:08:30</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>1887</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2701804046008034663</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:03:02</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>1889</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2701802712009026478</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-04-01 04:43:36</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>九大香型</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>1891</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>4502241938005026742</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-04-01 02:15:58</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>1893</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>4502236755002071934</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-04-01 01:26:05</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2701803867013013972</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-04-01 00:42:47</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>100</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>1898</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2701807753007027093</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-04-01 00:26:58</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>1900</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2701806564001010180</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-03-31 23:28:12</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>4502247337001013318</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-03-31 23:07:17</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>4502235601011032030</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:58:41</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>加赠金香鸭屎7g*1</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>清香桂花</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>4502240426001039235</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:39:23</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>1912</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2701797243198020465</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:33:09</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>1914</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2701791518183016163</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:28:41</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>加赠清香桂花7g*1</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>1916</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2701794542201032066</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:27:29</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>1918</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>4502237293002011335</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:08:02</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2701804839001105273</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:40:51</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>1923</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2701795803198009082</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:28:59</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>1926</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>4502222856174082946</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:04:42</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>1928</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>4502231029177043415</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:52:33</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>1930</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2701791698170013497</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:49:15</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>1932</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2701789968180015555</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:46:19</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>4502236214005003209</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:32:27</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>金香鸭屎+庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>1938</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>4502220447159030037</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:24:14</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>面值:面值F</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>1939</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>4502220267155015834</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:08:25</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>1942</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>4502218248180019946</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-03-31 18:03:23</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>1945</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>4502225019144020841</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:56:00</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>1947</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>4502220411171023639</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:30:05</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>庄园东方红</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>1949</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2701792491184017692</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:29:20</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>老丛私房姜花香</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>1951</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2701787304190017692</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:28:47</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*2</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>老丛私房宋种</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>1953</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2701791805182002151</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:17:12</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>1956</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2701791194162001761</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:13:34</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1  清香桂花7g*1</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>1959</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>4502214795157034930</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:10:02</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2701791015166049487</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-03-31 14:54:13</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1，老丛私房鸭屎7g*1</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2701799725170012660</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-03-31 14:50:42</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
         <v>1967</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>4502229770141180528</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>2026-03-31 14:37:43</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="inlineStr">
         <is>
           <t>加赠羊脂玉茶具（含公道杯）*1
 加赠 岽顶蜜兰香7g*2</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
+    <row r="119">
+      <c r="A119" s="1" t="n">
         <v>1970</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>4502216664156015647</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>2026-03-31 14:30:49</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="inlineStr">
         <is>
           <t>加赠岽顶蜜兰香7g*1</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
+    <row r="120">
+      <c r="A120" s="1" t="n">
         <v>1972</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>4502220229167110820</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>2026-03-31 13:59:40</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="inlineStr">
         <is>
           <t>加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
+    <row r="121">
+      <c r="A121" s="1" t="n">
         <v>1975</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>2701789068173038452</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>2026-03-31 13:44:04</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="inlineStr">
         <is>
           <t>加赠庄园鸭屎7g*1</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>悠山蜜兰</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
+    <row r="122">
+      <c r="A122" s="1" t="n">
         <v>1977</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>2701795081160041361</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>2026-03-31 13:00:53</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
         <is>
           <t>浓香芝兰</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
+    <row r="123">
+      <c r="A123" s="1" t="n">
         <v>1979</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>2701793605172097697</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>2026-03-31 12:46:08</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
+    <row r="124">
+      <c r="A124" s="1" t="n">
         <v>1981</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>4502222750168134701</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>2026-03-31 12:43:28</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr">
         <is>
           <t>加赠庄园鸭屎7g*1</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>金香鸭屎</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
+    <row r="125">
+      <c r="A125" s="1" t="n">
         <v>1983</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>2701791842174006875</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>2026-03-31 12:27:48</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="inlineStr">
         <is>
           <t>加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>老丛私房鸭屎香</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
+    <row r="126">
+      <c r="A126" s="1" t="n">
         <v>1985</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>2701785900152006875</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>2026-03-31 12:20:40</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
         <is>
           <t>面值:面值C</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
+    <row r="127">
+      <c r="A127" s="1" t="n">
         <v>1986</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>2701796773173023384</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>2026-03-31 12:17:46</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
         <is>
           <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
+    <row r="128">
+      <c r="A128" s="1" t="n">
         <v>1988</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>4502223792152007219</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>2026-03-31 11:53:25</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
         <is>
           <t>金香鸭屎</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
+    <row r="129">
+      <c r="A129" s="1" t="n">
         <v>1991</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>4502231425150001928</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>2026-03-31 11:46:41</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="inlineStr">
         <is>
           <t>加赠 庄园锯朵仔7g*1</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>六大香型300g</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
+    <row r="130">
+      <c r="A130" s="1" t="n">
         <v>1993</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>4502221452148014218</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>2026-03-31 10:55:00</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="inlineStr">
         <is>
           <t>加赠 清香桂花7g*1
 加赠 岽顶蜜兰香7g*1</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>金香鸭屎</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
+    <row r="131">
+      <c r="A131" s="1" t="n">
         <v>1996</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>2701796053176017380</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>2026-03-31 10:23:24</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D131" t="n">
         <v>100</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>加赠 岽顶蜜兰香7g*1</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
+    <row r="132">
+      <c r="A132" s="1" t="n">
         <v>1998</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>2701787700172003390</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>2026-03-31 10:10:59</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
         <is>
           <t>金香鸭屎</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
+    <row r="133">
+      <c r="A133" s="1" t="n">
         <v>2001</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>4502231461158061727</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>2026-03-31 09:16:40</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
         <is>
           <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
+    <row r="134">
+      <c r="A134" s="1" t="n">
         <v>2003</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>4502229590169143746</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>2026-03-31 09:14:26</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
+    <row r="135">
+      <c r="A135" s="1" t="n">
         <v>2005</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>2701790474159075985</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>2026-03-31 09:13:00</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
         <is>
           <t>金香鸭屎</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
+    <row r="136">
+      <c r="A136" s="1" t="n">
         <v>2007</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>2701791698144030571</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>2026-03-31 08:53:13</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="inlineStr">
         <is>
           <t>加赠庄园鸭屎7g*1</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>金香鸭屎</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
+    <row r="137">
+      <c r="A137" s="1" t="n">
         <v>2010</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>4502222355157017902</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>2026-03-31 06:38:51</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
         <is>
           <t>六大香型300g</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
+    <row r="138">
+      <c r="A138" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>2701794540172086884</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>2026-03-31 01:09:01</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
+    <row r="139">
+      <c r="A139" s="1" t="n">
         <v>2014</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>4502230778124054949</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>2026-03-31 00:43:06</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
         <is>
           <t>清香桂花</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
+    <row r="140">
+      <c r="A140" s="1" t="n">
         <v>2016</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>2701799583140013686</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>2026-03-31 00:00:06</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
         <is>
           <t>六大香型进阶版</t>
         </is>

--- a/old_send/db/new_df.xlsx
+++ b/old_send/db/new_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,124 +457,112 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>1412</v>
+        <v>1744</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4502247627136015243</t>
+          <t>4502270413153085649</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-06 23:30:03</t>
+          <t>2026-04-13 23:26:05</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>浓香芝兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1414</v>
+        <v>1748</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2701809696145090062</t>
+          <t>4502278872021051245</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-06 23:02:14</t>
+          <t>2026-04-13 23:22:27</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1417</v>
+        <v>1750</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2701810200126035688</t>
+          <t>4502277469161006430</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-06 22:47:41</t>
+          <t>2026-04-13 22:47:55</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>1420</v>
+        <v>1753</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4502245860138065144</t>
+          <t>2701831116132096988</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-06 22:22:15</t>
+          <t>2026-04-13 22:37:36</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>加赠老丛私房杏仁50g*1</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>庄园鸭屎+庄园锯朵仔</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>1426</v>
+        <v>1756</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4502252703120004329</t>
+          <t>4502278836021004302</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-04-06 22:16:44</t>
+          <t>2026-04-13 21:50:38</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -583,22 +571,22 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>清香桂花</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>1428</v>
+        <v>1758</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2701821361118079150</t>
+          <t>2701823808152016683</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-06 21:30:01</t>
+          <t>2026-04-13 20:34:29</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -606,27 +594,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>加赠老丛私房杏仁50g*1</t>
+          <t>加赠 羊脂玉茶具（含公道杯）*1
+加赠 庄园锯朵仔7g*1 庄园东方红7g*1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>1434</v>
+        <v>1764</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4502251008131085635</t>
+          <t>4502272681153001740</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-04-06 21:29:16</t>
+          <t>2026-04-13 20:30:14</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -635,22 +624,22 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>面值:面值C</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>1435</v>
+        <v>1767</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4502263789121030444</t>
+          <t>4502285894020020104</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-06 21:22:35</t>
+          <t>2026-04-13 20:27:34</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -665,44 +654,40 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>1436</v>
+        <v>1768</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4502255078120023938</t>
+          <t>2701840009137012951</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-06 21:16:36</t>
+          <t>2026-04-13 18:52:26</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>2.0高阶版</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>1439</v>
+        <v>1769</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4502261847139083625</t>
+          <t>2701830759132019697</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-06 21:07:23</t>
+          <t>2026-04-13 18:36:45</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -711,154 +696,146 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>1441</v>
+        <v>1771</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2701820065121005385</t>
+          <t>2701836879024060877</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04-06 21:04:23</t>
+          <t>2026-04-13 18:34:17</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>悠山蜜兰</t>
+          <t>庄园东方红</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>1443</v>
+        <v>1773</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4502255763121025635</t>
+          <t>4502277756015037121</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-06 18:09:39</t>
+          <t>2026-04-13 18:32:08</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>1446</v>
+        <v>1775</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4502257562117004220</t>
+          <t>2701836734013024491</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-04-06 17:36:12</t>
+          <t>2026-04-13 16:31:50</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>1448</v>
+        <v>1779</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2701821254128003472</t>
+          <t>4502284094015019621</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-06 17:12:27</t>
+          <t>2026-04-13 16:26:23</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>1452</v>
+        <v>1782</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4502248635124008544</t>
+          <t>4502284165012000440</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04-06 16:46:33</t>
+          <t>2026-04-13 16:25:00</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>悠山蜜兰</t>
+          <t>面值:面值B</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>1454</v>
+        <v>1783</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2701827337124027483</t>
+          <t>4502285461009004427</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:45</t>
+          <t>2026-04-13 16:16:48</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -867,50 +844,46 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>清香桂花</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>1459</v>
+        <v>1785</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4502258172117039314</t>
+          <t>2701828056134013490</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-04-06 15:31:12</t>
+          <t>2026-04-13 15:50:10</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>悠山蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>1461</v>
+        <v>1787</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4502256302121033042</t>
+          <t>2701839507006007893</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-04-06 15:20:00</t>
+          <t>2026-04-13 14:49:23</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -919,22 +892,22 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>1463</v>
+        <v>1790</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4502244996118005809</t>
+          <t>4502275922143002324</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-04-06 14:47:31</t>
+          <t>2026-04-13 13:55:11</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -949,116 +922,124 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>1465</v>
+        <v>1792</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2701823847107041053</t>
+          <t>4502280890127057439</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-06 14:21:10</t>
+          <t>2026-04-13 13:47:04</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>加赠 清香桂花7g*1</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>1469</v>
+        <v>1794</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2701816791127163860</t>
+          <t>2701829568107011375</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-04-06 14:06:07</t>
+          <t>2026-04-13 12:21:18</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>100</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>1472</v>
+        <v>1796</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2701821541096022380</t>
+          <t>2701834539109001853</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-04-06 12:08:55</t>
+          <t>2026-04-13 10:48:00</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>1474</v>
+        <v>1798</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4502256591103027525</t>
+          <t>2701828167115180092</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-04-06 11:00:58</t>
+          <t>2026-04-13 10:33:36</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>老丛私房东方红</t>
+          <t>老丛私房宋种</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>1477</v>
+        <v>1800</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4502258820098002931</t>
+          <t>2701833025117052881</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-04-06 10:28:16</t>
+          <t>2026-04-13 10:30:32</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1067,22 +1048,22 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>面值:面值B</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>1478</v>
+        <v>1801</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4502258388099002844</t>
+          <t>2701829172108003072</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-04-06 10:10:08</t>
+          <t>2026-04-13 10:15:47</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1091,22 +1072,22 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>悠山蜜兰</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>1480</v>
+        <v>1803</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2701819884087019685</t>
+          <t>2701834429114012254</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-04-06 09:56:08</t>
+          <t>2026-04-13 10:14:51</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1115,22 +1096,22 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>面值:面值B</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>1483</v>
+        <v>1804</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4502252991102002213</t>
+          <t>4502267136136021518</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-04-06 09:50:35</t>
+          <t>2026-04-13 09:57:05</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1138,83 +1119,75 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>加赠 庄园锯朵仔7g*1</t>
+          <t>加赠金香鸭屎7g*1</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>1485</v>
+        <v>1806</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2701813152086040777</t>
+          <t>4502269801129004830</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-04-06 08:32:10</t>
+          <t>2026-04-13 09:22:19</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>四大老丛</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>1487</v>
+        <v>1809</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2701819995096027266</t>
+          <t>2701832052104060178</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-04-06 08:01:35</t>
+          <t>2026-04-13 07:46:55</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>1490</v>
+        <v>1811</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2701818841101054094</t>
+          <t>2701832775109006476</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-04-06 08:00:26</t>
+          <t>2026-04-13 07:20:08</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1223,46 +1196,50 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>面值:面值B</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>1491</v>
+        <v>1813</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2701821146100006762</t>
+          <t>2701825035119006686</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-04-06 07:29:30</t>
+          <t>2026-04-13 02:51:19</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>100</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*4加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>悠山蜜兰</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>1493</v>
+        <v>1817</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2701826689096018375</t>
+          <t>2701839109108019472</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-04-06 07:00:19</t>
+          <t>2026-04-13 01:22:48</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1271,50 +1248,46 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>1495</v>
+        <v>1819</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4502252988090021627</t>
+          <t>2701824024124008953</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-04-06 02:57:11</t>
+          <t>2026-04-13 01:11:54</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>庄园东方红</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>1498</v>
+        <v>1821</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2701814631097020172</t>
+          <t>2701827624111023582</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-04-06 01:35:23</t>
+          <t>2026-04-13 00:59:23</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1323,22 +1296,22 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>1500</v>
+        <v>1824</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2701819777104109098</t>
+          <t>4502273724113008605</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-04-06 00:01:46</t>
+          <t>2026-04-13 00:45:40</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1347,79 +1320,70 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>1502</v>
+        <v>1827</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2701826581086026461</t>
+          <t>4502263719148000315</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-04-05 23:56:30</t>
+          <t>2026-04-13 00:03:29</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>加赠 羊脂玉茶具（含公道杯）*1
-加赠 庄园鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>1505</v>
+        <v>1831</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4502255436101023916</t>
+          <t>4502280170121122439</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-04-05 23:37:14</t>
+          <t>2026-04-13 00:00:43</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>100</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>1511</v>
+        <v>1834</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2701820390109053971</t>
+          <t>2701833351092063796</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-04-05 23:00:59</t>
+          <t>2026-04-12 23:30:03</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1428,22 +1392,22 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>金香鸭屎+庄园蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>1514</v>
+        <v>1836</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2701823197088060699</t>
+          <t>2701828202115012592</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-04-05 22:45:36</t>
+          <t>2026-04-12 23:29:09</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1452,22 +1416,22 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>庄园东方红</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>1516</v>
+        <v>1839</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2701810632098007668</t>
+          <t>4502264076126015034</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-04-05 21:46:38</t>
+          <t>2026-04-12 23:29:07</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1476,22 +1440,22 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>1518</v>
+        <v>1841</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4502261559092010042</t>
+          <t>2701825176098051365</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-04-05 21:30:16</t>
+          <t>2026-04-12 23:28:38</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1499,128 +1463,131 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>加赠 羊脂玉茶具（含公道杯）*1</t>
+          <t>加赠庄园鸭屎7g*1</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>四大老丛</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>1520</v>
+        <v>1843</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2701821145083193696</t>
+          <t>4502269407113036317</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-04-05 20:41:55</t>
+          <t>2026-04-12 23:18:38</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>老丛私房鸭屎香</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>1522</v>
+        <v>1845</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4502260911083104041</t>
+          <t>4502277327110014238</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-04-05 19:52:16</t>
+          <t>2026-04-12 22:33:21</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>加赠 羊脂玉茶具（含公道杯）*1
-加赠 庄园鸭屎7g*1</t>
+          <t>加赠庄园蜜兰7g*1</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>1525</v>
+        <v>1847</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4502261559089013539</t>
+          <t>2701826295103062095</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-04-05 19:44:38</t>
+          <t>2026-04-12 21:27:37</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>1528</v>
+        <v>1849</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4502249424075010504</t>
+          <t>2701824134112038061</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-04-05 18:58:17</t>
+          <t>2026-04-12 20:49:13</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园东方红</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>1532</v>
+        <v>1851</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4502253710086028711</t>
+          <t>2701828058111019697</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-04-05 18:25:11</t>
+          <t>2026-04-12 20:48:51</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1635,16 +1602,16 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>1534</v>
+        <v>1853</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4502249067089004645</t>
+          <t>2701823988122028879</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-04-05 17:55:19</t>
+          <t>2026-04-12 20:47:00</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1653,22 +1620,22 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>1537</v>
+        <v>1855</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4502246475106076047</t>
+          <t>2701831117104074186</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-04-05 16:32:29</t>
+          <t>2026-04-12 20:24:30</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1677,134 +1644,140 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>1540</v>
+        <v>1857</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2701817187081000176</t>
+          <t>4502274084124021734</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-04-05 15:57:34</t>
+          <t>2026-04-12 19:41:40</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>100</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>1541</v>
+        <v>1859</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2701812756071055367</t>
+          <t>4502276390108075119</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-04-05 15:55:40</t>
+          <t>2026-04-12 19:38:31</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">发顺丰
-加赠 庄园蜜兰7g*2
-</t>
+          <t>加赠庄园蜜兰7g*1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>1542</v>
+        <v>1861</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2701813152076010182</t>
+          <t>4502274519111006212</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-04-05 15:55:32</t>
+          <t>2026-04-12 17:37:06</t>
         </is>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>1544</v>
+        <v>1865</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2701824457081003262</t>
+          <t>4502273724101037541</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-04-05 15:46:24</t>
+          <t>2026-04-12 17:28:46</t>
         </is>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>加赠 岽顶蜜兰香7g*1</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>1547</v>
+        <v>1867</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2701812146080007394</t>
+          <t>4502271567127000427</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-04-05 14:15:21</t>
+          <t>2026-04-12 17:18:17</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -1813,40 +1786,45 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>1549</v>
+        <v>1869</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2701816500081017484</t>
+          <t>4502275779109032032</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-04-05 13:22:41</t>
+          <t>2026-04-12 16:26:49</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>加赠 羊脂玉茶具（含公道杯）*1
+加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>老丛私房鸭屎香</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>1551</v>
+        <v>1871</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2701820245070021359</t>
+          <t>4502277865112005204</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-04-05 12:46:18</t>
+          <t>2026-04-12 16:25:25</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1855,46 +1833,50 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>面值:面值B</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>1553</v>
+        <v>1872</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4502259543073009312</t>
+          <t>4502263287125007312</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-04-05 11:46:38</t>
+          <t>2026-04-12 16:21:22</t>
         </is>
       </c>
       <c r="D57" t="n">
         <v>0</v>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>加赠 清香桂花7g*1</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>1555</v>
+        <v>1874</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4502264078072045322</t>
+          <t>2701827087106000153</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-04-05 11:45:02</t>
+          <t>2026-04-12 16:13:42</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1903,50 +1885,46 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>1557</v>
+        <v>1876</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4502251657089007242</t>
+          <t>4502275922114015546</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-04-05 11:06:16</t>
+          <t>2026-04-12 15:41:21</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>加赠 羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>1560</v>
+        <v>1880</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4502248092074011137</t>
+          <t>4502280133098029043</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-04-05 09:59:33</t>
+          <t>2026-04-12 14:43:07</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -1955,84 +1933,80 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>面值:面值B</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>1561</v>
+        <v>1882</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2701814124067039452</t>
+          <t>4502273724094050024</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-04-05 09:16:16</t>
+          <t>2026-04-12 14:02:13</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>加赠 岽顶蜜兰香7g*1</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>1564</v>
+        <v>1884</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4502249895073074817</t>
+          <t>2701826112089028575</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-04-05 08:21:58</t>
+          <t>2026-04-12 13:55:55</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>100</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>顾客送礼 需要检查好包装</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>1567</v>
+        <v>1886</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2701818805076011799</t>
+          <t>4502270161113027435</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-04-05 06:53:32</t>
+          <t>2026-04-12 13:37:24</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -2041,16 +2015,16 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>1571</v>
+        <v>1889</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2701815672075000561</t>
+          <t>4502262456104027435</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-04-05 06:46:18</t>
+          <t>2026-04-12 13:36:40</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2059,22 +2033,22 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>面值:面值B</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>1573</v>
+        <v>1890</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2701809696092038193</t>
+          <t>4502275345104025940</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-04-05 02:47:24</t>
+          <t>2026-04-12 13:32:14</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2083,29 +2057,208 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>1575</v>
+        <v>1892</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2701814631070035563</t>
+          <t>4502282510101015608</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-04-05 00:13:28</t>
+          <t>2026-04-12 13:12:40</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2701838173079052075</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-04-12 13:06:08</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>1899</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2701825250095097982</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-04-12 12:48:43</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2701829499090004550</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-04-12 11:06:05</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>加赠 清香桂花7g*1</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>4502279773096018042</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-04-12 09:37:54</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>100</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>按备注发货 实际发：
+庄园蜜兰50g*10（不需要铝罐 只需要外面黑色纸盒包装）
+庄园蜜兰7g*1
+取茶三件套*1</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2701827554070007470</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-04-12 08:14:40</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>1910</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2701826976072027798</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-04-12 07:58:22</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>面值:面值C</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>1911</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2701839685069077594</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-04-12 07:40:55</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
         <is>
           <t>六大香型300g</t>
         </is>

--- a/old_send/db/new_df.xlsx
+++ b/old_send/db/new_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,16 +457,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>1744</v>
+        <v>1089</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4502270413153085649</t>
+          <t>4502303715082033214</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-13 23:26:05</t>
+          <t>2026-04-18 23:45:48</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -475,22 +475,22 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1748</v>
+        <v>1092</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4502278872021051245</t>
+          <t>2701859845125000891</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-13 23:22:27</t>
+          <t>2026-04-18 23:35:39</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -499,22 +499,22 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1750</v>
+        <v>1095</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4502277469161006430</t>
+          <t>4502307205090043936</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-13 22:47:55</t>
+          <t>2026-04-18 23:05:29</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -523,22 +523,22 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>1753</v>
+        <v>1099</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2701831116132096988</t>
+          <t>4502303355095082608</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-13 22:37:36</t>
+          <t>2026-04-18 22:49:27</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -553,117 +553,124 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>1756</v>
+        <v>1101</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4502278836021004302</t>
+          <t>2701862727103136359</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-04-13 21:50:38</t>
+          <t>2026-04-18 22:18:09</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>1758</v>
+        <v>1103</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2701823808152016683</t>
+          <t>2701861143098015556</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-13 20:34:29</t>
+          <t>2026-04-18 21:32:55</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>100</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>加赠 羊脂玉茶具（含公道杯）*1
-加赠 庄园锯朵仔7g*1 庄园东方红7g*1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>1764</v>
+        <v>1105</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4502272681153001740</t>
+          <t>2701857144093023074</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-04-13 20:30:14</t>
+          <t>2026-04-18 21:17:07</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>1767</v>
+        <v>1107</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4502285894020020104</t>
+          <t>4502310985073007022</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-13 20:27:34</t>
+          <t>2026-04-18 21:09:32</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>面值:面值C</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>1768</v>
+        <v>1109</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2701840009137012951</t>
+          <t>2701853618125011655</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-13 18:52:26</t>
+          <t>2026-04-18 21:09:30</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -672,22 +679,22 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.0高阶版</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>1769</v>
+        <v>1111</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2701830759132019697</t>
+          <t>2701863265087006092</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-13 18:36:45</t>
+          <t>2026-04-18 19:47:01</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -696,70 +703,78 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>1771</v>
+        <v>1113</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2701836879024060877</t>
+          <t>4502296836069050522</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04-13 18:34:17</t>
+          <t>2026-04-18 19:34:51</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>庄园东方红</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>1773</v>
+        <v>1116</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4502277756015037121</t>
+          <t>4502309400078030523</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-13 18:32:08</t>
+          <t>2026-04-18 19:34:44</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>1775</v>
+        <v>1119</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2701836734013024491</t>
+          <t>2701858226101006499</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-04-13 16:31:50</t>
+          <t>2026-04-18 18:50:16</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -768,74 +783,74 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>1779</v>
+        <v>1122</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4502284094015019621</t>
+          <t>4502313866076149746</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-13 16:26:23</t>
+          <t>2026-04-18 18:40:59</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>老丛私房鸭屎香</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>1782</v>
+        <v>1124</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4502284165012000440</t>
+          <t>2701868125093000691</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04-13 16:25:00</t>
+          <t>2026-04-18 18:27:56</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>面值:面值B</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>1783</v>
+        <v>1127</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4502285461009004427</t>
+          <t>4502311310084008047</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-04-13 16:16:48</t>
+          <t>2026-04-18 18:16:41</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -844,70 +859,78 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>1785</v>
+        <v>1131</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2701828056134013490</t>
+          <t>4502305226089046432</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-04-13 15:50:10</t>
+          <t>2026-04-18 17:56:15</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>十年陈窖藏鸭屎香</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>1787</v>
+        <v>1134</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2701839507006007893</t>
+          <t>2701860709111012593</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-04-13 14:49:23</t>
+          <t>2026-04-18 17:44:14</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>清香桂花</t>
+          <t>庄园鸭屎+岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>1790</v>
+        <v>1137</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4502275922143002324</t>
+          <t>4502314118068028238</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-04-13 13:55:11</t>
+          <t>2026-04-18 17:14:08</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -922,16 +945,16 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>1792</v>
+        <v>1139</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4502280890127057439</t>
+          <t>4502311056070007307</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-13 13:47:04</t>
+          <t>2026-04-18 16:55:39</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -939,155 +962,159 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>加赠 清香桂花7g*1</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1加赠庄园鸭屎7*1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>1794</v>
+        <v>1142</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2701829568107011375</t>
+          <t>4502311526081025245</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-04-13 12:21:18</t>
+          <t>2026-04-18 16:52:11</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>四大老丛</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>1796</v>
+        <v>1144</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2701834539109001853</t>
+          <t>2701858188096032879</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-04-13 10:48:00</t>
+          <t>2026-04-18 16:38:01</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>1798</v>
+        <v>1146</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2701828167115180092</t>
+          <t>2701851422104037871</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-04-13 10:33:36</t>
+          <t>2026-04-18 14:52:26</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>老丛私房宋种</t>
+          <t>面值:面值C</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>1800</v>
+        <v>1147</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2701833025117052881</t>
+          <t>4502317861066120509</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-04-13 10:30:32</t>
+          <t>2026-04-18 14:39:44</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>面值:面值B</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>1801</v>
+        <v>1149</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2701829172108003072</t>
+          <t>2701858623088026897</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-04-13 10:15:47</t>
+          <t>2026-04-18 14:38:58</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>加赠金香鸭屎7g*1，浓香芝兰7g*1</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>悠山蜜兰</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>1803</v>
+        <v>1151</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2701834429114012254</t>
+          <t>4502313685061001843</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-04-13 10:14:51</t>
+          <t>2026-04-18 14:34:27</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1096,50 +1123,46 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>面值:面值B</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>1804</v>
+        <v>1154</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4502267136136021518</t>
+          <t>4502311489066028645</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-04-13 09:57:05</t>
+          <t>2026-04-18 13:32:36</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>加赠金香鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>1806</v>
+        <v>1156</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4502269801129004830</t>
+          <t>2701856571083014555</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-04-13 09:22:19</t>
+          <t>2026-04-18 12:55:34</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1154,16 +1177,16 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>1809</v>
+        <v>1158</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2701832052104060178</t>
+          <t>4502309871068110410</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-04-13 07:46:55</t>
+          <t>2026-04-18 11:33:23</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1172,74 +1195,74 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>1811</v>
+        <v>1160</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2701832775109006476</t>
+          <t>4502313686055022233</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-04-13 07:20:08</t>
+          <t>2026-04-18 10:56:48</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>1813</v>
+        <v>1164</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2701825035119006686</t>
+          <t>2701853943088064653</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-04-13 02:51:19</t>
+          <t>2026-04-18 10:46:56</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>加赠老丛私房杏仁50g*4加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>1817</v>
+        <v>1168</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2701839109108019472</t>
+          <t>2701862401075028984</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-04-13 01:22:48</t>
+          <t>2026-04-18 10:44:31</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1254,40 +1277,44 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>1819</v>
+        <v>1170</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2701824024124008953</t>
+          <t>2701856894073000070</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-04-13 01:11:54</t>
+          <t>2026-04-18 10:10:19</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>老丛私房凹富后</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>1821</v>
+        <v>1174</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2701827624111023582</t>
+          <t>4502314081062075127</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-04-13 00:59:23</t>
+          <t>2026-04-18 09:36:21</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1302,16 +1329,16 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>1824</v>
+        <v>1176</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4502273724113008605</t>
+          <t>4502319230050028708</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-04-13 00:45:40</t>
+          <t>2026-04-18 09:31:21</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1320,22 +1347,22 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>1827</v>
+        <v>1179</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4502263719148000315</t>
+          <t>2701859233080218274</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-04-13 00:03:29</t>
+          <t>2026-04-18 09:11:16</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1344,22 +1371,22 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>1831</v>
+        <v>1181</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4502280170121122439</t>
+          <t>4502313399057002203</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-04-13 00:00:43</t>
+          <t>2026-04-18 01:32:22</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1368,22 +1395,22 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>1834</v>
+        <v>1184</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2701833351092063796</t>
+          <t>4502315558050014028</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-04-12 23:30:03</t>
+          <t>2026-04-18 01:21:00</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1392,22 +1419,22 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>1836</v>
+        <v>1187</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2701828202115012592</t>
+          <t>4502311489054014931</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-04-12 23:29:09</t>
+          <t>2026-04-18 01:18:19</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1416,22 +1443,22 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>金香鸭屎+清香桂花</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>1839</v>
+        <v>1190</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4502264076126015034</t>
+          <t>2701859413073007779</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-04-12 23:29:07</t>
+          <t>2026-04-18 00:34:15</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1440,827 +1467,37 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>1841</v>
+        <v>1192</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2701825176098051365</t>
+          <t>2701864021066031094</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-04-12 23:28:38</t>
+          <t>2026-04-18 00:04:07</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>加赠庄园鸭屎7g*1</t>
+          <t xml:space="preserve">加赠 羊脂玉茶具（含公道杯）*1
+加赠 庄园鸭屎7g*2
+</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>1843</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>4502269407113036317</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2026-04-12 23:18:38</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>100</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>六大香型进阶版</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>1845</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>4502277327110014238</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2026-04-12 22:33:21</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>100</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>1847</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2701826295103062095</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2026-04-12 21:27:37</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>1849</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2701824134112038061</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2026-04-12 20:49:13</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>100</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>庄园东方红</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>1851</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2701828058111019697</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2026-04-12 20:48:51</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>1853</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2701823988122028879</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2026-04-12 20:47:00</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>金香鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>1855</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2701831117104074186</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2026-04-12 20:24:30</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
           <t>岽顶蜜兰香</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>1857</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>4502274084124021734</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2026-04-12 19:41:40</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>1859</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>4502276390108075119</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2026-04-12 19:38:31</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>金香鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>1861</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>4502274519111006212</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2026-04-12 17:37:06</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>加赠 岽顶蜜兰香7g*1</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>1865</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>4502273724101037541</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2026-04-12 17:28:46</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>1867</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>4502271567127000427</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2026-04-12 17:18:17</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>加赠 岽顶蜜兰香7g*1</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>1869</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>4502275779109032032</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2026-04-12 16:26:49</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>100</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>加赠 羊脂玉茶具（含公道杯）*1
-加赠 岽顶蜜兰香7g*1</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>老丛私房鸭屎香</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>1871</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>4502277865112005204</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2026-04-12 16:25:25</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>面值:面值B</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>1872</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>4502263287125007312</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2026-04-12 16:21:22</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>加赠 清香桂花7g*1</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>金香鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>1874</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2701827087106000153</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2026-04-12 16:13:42</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>六大香型进阶版</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>1876</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>4502275922114015546</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2026-04-12 15:41:21</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>1880</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>4502280133098029043</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2026-04-12 14:43:07</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>六大香型进阶版</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>1882</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>4502273724094050024</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2026-04-12 14:02:13</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>1884</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2701826112089028575</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2026-04-12 13:55:55</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>1886</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>4502270161113027435</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2026-04-12 13:37:24</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>100</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>1889</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>4502262456104027435</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2026-04-12 13:36:40</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>面值:面值B</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>1890</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>4502275345104025940</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2026-04-12 13:32:14</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>金香鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>1892</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>4502282510101015608</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2026-04-12 13:12:40</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>100</v>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>金香鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>1895</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2701838173079052075</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2026-04-12 13:06:08</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>1899</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2701825250095097982</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2026-04-12 12:48:43</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>1901</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2701829499090004550</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2026-04-12 11:06:05</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>加赠 清香桂花7g*1</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>庄园蜜兰</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>1903</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>4502279773096018042</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2026-04-12 09:37:54</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>100</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>按备注发货 实际发：
-庄园蜜兰50g*10（不需要铝罐 只需要外面黑色纸盒包装）
-庄园蜜兰7g*1
-取茶三件套*1</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>庄园蜜兰</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>1906</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2701827554070007470</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>2026-04-12 08:14:40</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>岽顶蜜兰香</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="n">
-        <v>1910</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2701826976072027798</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>2026-04-12 07:58:22</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>面值:面值C</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>1911</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2701839685069077594</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2026-04-12 07:40:55</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>六大香型300g</t>
         </is>
       </c>
     </row>

--- a/old_send/db/new_df.xlsx
+++ b/old_send/db/new_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,16 +457,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>1089</v>
+        <v>863</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4502303715082033214</t>
+          <t>4502312568012018248</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-18 23:45:48</t>
+          <t>2026-04-20 23:41:49</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -481,70 +481,79 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1092</v>
+        <v>865</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2701859845125000891</t>
+          <t>2701862906014001381</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-18 23:35:39</t>
+          <t>2026-04-20 23:21:15</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园东方红</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1095</v>
+        <v>868</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4502307205090043936</t>
+          <t>2701867910013001381</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-18 23:05:29</t>
+          <t>2026-04-20 23:20:19</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>面值:面值B</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>1099</v>
+        <v>869</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4502303355095082608</t>
+          <t>2701877269018014652</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-18 22:49:27</t>
+          <t>2026-04-20 23:19:27</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1
+加赠咖啡色两罐装礼袋*1</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>金香鸭屎</t>
@@ -553,44 +562,40 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>1101</v>
+        <v>871</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2701862727103136359</t>
+          <t>4502322291008013202</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-04-18 22:18:09</t>
+          <t>2026-04-20 23:18:12</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>1103</v>
+        <v>875</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2701861143098015556</t>
+          <t>4502301807161074531</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-18 21:32:55</t>
+          <t>2026-04-20 23:16:52</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -599,102 +604,98 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>1105</v>
+        <v>878</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2701857144093023074</t>
+          <t>2701867515007073754</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-04-18 21:17:07</t>
+          <t>2026-04-20 23:04:00</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>加赠 庄园锯朵仔7g*1</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>1107</v>
+        <v>879</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4502310985073007022</t>
+          <t>2701864023014235585</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-18 21:09:32</t>
+          <t>2026-04-20 22:43:41</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>1109</v>
+        <v>880</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2701853618125011655</t>
+          <t>2701864023014153566</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-18 21:09:30</t>
+          <t>2026-04-20 22:43:41</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>1111</v>
+        <v>883</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2701863265087006092</t>
+          <t>2701869891006031757</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-18 19:47:01</t>
+          <t>2026-04-20 22:14:49</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -703,50 +704,46 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>1113</v>
+        <v>888</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4502296836069050522</t>
+          <t>2701873453010014950</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04-18 19:34:51</t>
+          <t>2026-04-20 22:13:17</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>1116</v>
+        <v>891</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4502309400078030523</t>
+          <t>4502312460016023709</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-18 19:34:44</t>
+          <t>2026-04-20 22:00:47</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -754,27 +751,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>加赠庄园蜜兰7g*1</t>
+          <t>加赠 庄园锯朵仔7g*1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>1119</v>
+        <v>893</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2701858226101006499</t>
+          <t>2701863732008020172</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-04-18 18:50:16</t>
+          <t>2026-04-20 21:37:34</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -789,16 +786,16 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>1122</v>
+        <v>895</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4502313866076149746</t>
+          <t>2701862436016002764</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-18 18:40:59</t>
+          <t>2026-04-20 21:30:01</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -807,50 +804,46 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>老丛私房鸭屎香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>1124</v>
+        <v>898</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2701868125093000691</t>
+          <t>4502313399146016234</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04-18 18:27:56</t>
+          <t>2026-04-20 20:05:33</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>1127</v>
+        <v>900</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4502311310084008047</t>
+          <t>2701871763006009378</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-04-18 18:16:41</t>
+          <t>2026-04-20 20:04:41</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -859,22 +852,22 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>1131</v>
+        <v>902</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4502305226089046432</t>
+          <t>4502301480142044642</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-04-18 17:56:15</t>
+          <t>2026-04-20 19:34:28</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -882,135 +875,133 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>加赠老丛私房杏仁50g*1加赠 庄园锯朵仔7g*1</t>
+          <t>加赠金香鸭屎7g*1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>十年陈窖藏鸭屎香</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>1134</v>
+        <v>904</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2701860709111012593</t>
+          <t>4502321643007017503</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-04-18 17:44:14</t>
+          <t>2026-04-20 19:09:20</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>庄园鸭屎+岽顶蜜兰香</t>
+          <t>浓香芝兰</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>1137</v>
+        <v>906</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4502314118068028238</t>
+          <t>4502326358006017442</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-04-18 17:14:08</t>
+          <t>2026-04-20 18:25:11</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>1139</v>
+        <v>910</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4502311056070007307</t>
+          <t>4502323801003020649</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-18 16:55:39</t>
+          <t>2026-04-20 18:25:03</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1加赠庄园鸭屎7*1</t>
+          <t>加赠 老丛私房八仙30g*1
+加赠 老丛私房凹富后30g*1
+（用50g罐子装着发货）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>老丛私房宋种</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>1142</v>
+        <v>914</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4502311526081025245</t>
+          <t>4502310985146003003</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-04-18 16:52:11</t>
+          <t>2026-04-20 18:22:01</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>四大老丛</t>
+          <t>面值:面值C</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>1144</v>
+        <v>915</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2701858188096032879</t>
+          <t>4502316494120032124</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-04-18 16:38:01</t>
+          <t>2026-04-20 17:03:23</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1019,22 +1010,22 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>1146</v>
+        <v>917</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2701851422104037871</t>
+          <t>4502315379013214526</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-04-18 14:52:26</t>
+          <t>2026-04-20 16:55:55</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1043,22 +1034,22 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>面值:面值C</t>
+          <t>面值:面值B</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>1147</v>
+        <v>918</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4502317861066120509</t>
+          <t>2701856964181003999</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-04-18 14:39:44</t>
+          <t>2026-04-20 16:54:57</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1066,7 +1057,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>加赠庄园蜜兰7g*1</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1077,16 +1068,16 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>1149</v>
+        <v>923</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2701858623088026897</t>
+          <t>2701862508004010798</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-04-18 14:38:58</t>
+          <t>2026-04-20 16:54:22</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1094,51 +1085,55 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>加赠金香鸭屎7g*1，浓香芝兰7g*1</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>1151</v>
+        <v>925</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4502313685061001843</t>
+          <t>4502310699155008100</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-04-18 14:34:27</t>
+          <t>2026-04-20 15:40:32</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>1154</v>
+        <v>928</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4502311489066028645</t>
+          <t>4502307133133091420</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-04-18 13:32:36</t>
+          <t>2026-04-20 14:04:50</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1147,98 +1142,98 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>浓香芝兰</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>1156</v>
+        <v>930</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2701856571083014555</t>
+          <t>4502318798133010449</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-04-18 12:55:34</t>
+          <t>2026-04-20 13:38:44</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>1158</v>
+        <v>932</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4502309871068110410</t>
+          <t>2701851060157004262</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-04-18 11:33:23</t>
+          <t>2026-04-20 13:18:31</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>清香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>1160</v>
+        <v>936</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4502313686055022233</t>
+          <t>2701854840161029970</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-04-18 10:56:48</t>
+          <t>2026-04-20 12:40:20</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>1164</v>
+        <v>939</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2701853943088064653</t>
+          <t>4502309727120027322</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-04-18 10:46:56</t>
+          <t>2026-04-20 12:35:07</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1253,16 +1248,16 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>1168</v>
+        <v>943</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2701862401075028984</t>
+          <t>4502306269139047714</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-04-18 10:44:31</t>
+          <t>2026-04-20 12:25:30</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1277,44 +1272,44 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>1170</v>
+        <v>945</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2701856894073000070</t>
+          <t>2701853436146010798</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-04-18 10:10:19</t>
+          <t>2026-04-20 11:30:50</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>加赠老丛私房杏仁50g*1</t>
+          <t>发顺丰空运</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>老丛私房凹富后</t>
+          <t>金香鸭屎+庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>1174</v>
+        <v>948</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4502314081062075127</t>
+          <t>2701863157156010798</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-04-18 09:36:21</t>
+          <t>2026-04-20 11:28:35</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1323,70 +1318,79 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>面值:面值B</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>1176</v>
+        <v>949</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4502319230050028708</t>
+          <t>2701851528152019357</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-04-18 09:31:21</t>
+          <t>2026-04-20 10:23:03</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>加赠：庄园蜜兰7g*2 咖啡色两罐装礼袋*2
+发顺丰</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>1179</v>
+        <v>950</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2701859233080218274</t>
+          <t>2701865065156070450</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-04-18 09:11:16</t>
+          <t>2026-04-20 10:12:19</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>加赠岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>1181</v>
+        <v>952</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4502313399057002203</t>
+          <t>2701866901147022371</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-04-18 01:32:22</t>
+          <t>2026-04-20 09:47:34</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1395,46 +1399,50 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>1184</v>
+        <v>954</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4502315558050014028</t>
+          <t>2701862151138010492</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-04-18 01:21:00</t>
+          <t>2026-04-20 09:19:55</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>1187</v>
+        <v>956</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4502311489054014931</t>
+          <t>2701868629159005574</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-04-18 01:18:19</t>
+          <t>2026-04-20 02:14:01</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1443,22 +1451,22 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>金香鸭屎+清香桂花</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>1190</v>
+        <v>958</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2701859413073007779</t>
+          <t>4502304252117005341</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-04-18 00:34:15</t>
+          <t>2026-04-20 00:36:44</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1467,37 +1475,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>1192</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2701864021066031094</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2026-04-18 00:04:07</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>100</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">加赠 羊脂玉茶具（含公道杯）*1
-加赠 庄园鸭屎7g*2
-</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>岽顶蜜兰香</t>
+          <t>面值:面值C</t>
         </is>
       </c>
     </row>

--- a/old_send/db/new_df.xlsx
+++ b/old_send/db/new_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,16 +457,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>863</v>
+        <v>1717</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4502312568012018248</t>
+          <t>5112523442049028326</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-20 23:41:49</t>
+          <t>2026-04-27 23:54:09</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -475,22 +475,22 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>865</v>
+        <v>1719</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2701862906014001381</t>
+          <t>5112519986076166714</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-20 23:21:15</t>
+          <t>2026-04-27 23:47:21</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -498,86 +498,89 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+          <t>加赠 庄园锯朵仔7g*1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>庄园东方红</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>868</v>
+        <v>1721</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2701867910013001381</t>
+          <t>3298296507645009591</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-20 23:20:19</t>
+          <t>2026-04-27 23:22:51</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>面值:面值B</t>
+          <t>金香鸭屎+庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>869</v>
+        <v>1724</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2701877269018014652</t>
+          <t>5112805429760005606</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-20 23:19:27</t>
+          <t>2026-04-27 23:19:49</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1
-加赠咖啡色两罐装礼袋*1</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>871</v>
+        <v>1729</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4502322291008013202</t>
+          <t>3298771237572157084</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-04-20 23:18:12</t>
+          <t>2026-04-27 23:14:10</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -586,16 +589,16 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>875</v>
+        <v>1731</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4502301807161074531</t>
+          <t>3298295283496021075</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-20 23:16:52</t>
+          <t>2026-04-27 23:14:04</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -604,22 +607,22 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>878</v>
+        <v>1733</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2701867515007073754</t>
+          <t>5112726408581127828</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-04-20 23:04:00</t>
+          <t>2026-04-27 22:59:20</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -628,22 +631,22 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>879</v>
+        <v>1735</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2701864023014235585</t>
+          <t>5112514442110019507</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-20 22:43:41</t>
+          <t>2026-04-27 22:45:23</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -652,74 +655,74 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>880</v>
+        <v>1737</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2701864023014153566</t>
+          <t>3298332686002021276</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-20 22:43:41</t>
+          <t>2026-04-27 22:32:08</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>清香桂花</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>883</v>
+        <v>1740</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2701869891006031757</t>
+          <t>3298291575757240996</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-20 22:14:49</t>
+          <t>2026-04-27 22:26:34</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>悠山蜜兰</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>888</v>
+        <v>1742</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2701873453010014950</t>
+          <t>5112509978019130530</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04-20 22:13:17</t>
+          <t>2026-04-27 22:05:23</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -728,74 +731,70 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>891</v>
+        <v>1744</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4502312460016023709</t>
+          <t>3298326062360055354</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-20 22:00:47</t>
+          <t>2026-04-27 21:41:36</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>加赠 庄园锯朵仔7g*1</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>悠山蜜兰</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>893</v>
+        <v>1746</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2701863732008020172</t>
+          <t>5112505190676074648</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-04-20 21:37:34</t>
+          <t>2026-04-27 21:27:37</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>895</v>
+        <v>1750</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2701862436016002764</t>
+          <t>5112711648883129839</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-20 21:30:01</t>
+          <t>2026-04-27 21:26:10</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -804,22 +803,22 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>面值:面值F</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>898</v>
+        <v>1751</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4502313399146016234</t>
+          <t>5112797257142002615</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04-20 20:05:33</t>
+          <t>2026-04-27 21:25:09</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -828,22 +827,22 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>900</v>
+        <v>1754</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2701871763006009378</t>
+          <t>5112709704142072014</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-04-20 20:04:41</t>
+          <t>2026-04-27 21:05:49</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -852,50 +851,46 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>902</v>
+        <v>1756</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4502301480142044642</t>
+          <t>3298909656231001962</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-04-20 19:34:28</t>
+          <t>2026-04-27 20:44:28</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>加赠金香鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>悠山蜜兰</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>904</v>
+        <v>1758</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4502321643007017503</t>
+          <t>3298907496459088759</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-04-20 19:09:20</t>
+          <t>2026-04-27 20:43:47</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -904,80 +899,74 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>浓香芝兰</t>
+          <t>十年陈窖藏蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>906</v>
+        <v>1761</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4502326358006017442</t>
+          <t>3298304966989028575</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-04-20 18:25:11</t>
+          <t>2026-04-27 19:59:54</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>加赠老丛私房杏仁50g*1</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>910</v>
+        <v>1763</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4502323801003020649</t>
+          <t>5112687708374004315</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-20 18:25:03</t>
+          <t>2026-04-27 19:30:11</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>加赠 老丛私房八仙30g*1
-加赠 老丛私房凹富后30g*1
-（用50g罐子装着发货）</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>老丛私房宋种</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>914</v>
+        <v>1766</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4502310985146003003</t>
+          <t>3298297982545013493</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-04-20 18:22:01</t>
+          <t>2026-04-27 19:16:37</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -986,46 +975,50 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>面值:面值C</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>915</v>
+        <v>1768</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4502316494120032124</t>
+          <t>5112293943305001921</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-04-20 17:03:23</t>
+          <t>2026-04-27 19:02:50</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>917</v>
+        <v>1770</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4502315379013214526</t>
+          <t>3298881036207024386</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-04-20 16:55:55</t>
+          <t>2026-04-27 18:16:54</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1034,22 +1027,22 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>面值:面值B</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>918</v>
+        <v>1773</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2701856964181003999</t>
+          <t>3298293410900024386</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-04-20 16:54:57</t>
+          <t>2026-04-27 17:55:26</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1057,55 +1050,55 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+          <t>加赠 老丛私房杏仁50g*2
+ 加赠 羊脂玉茶具（含公道杯）*1
+加赠 岽顶蜜兰香7g*1
+加赠 庄园锯朵仔7g*1
+加赠 十年陈鸭屎香7g*1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>923</v>
+        <v>1776</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2701862508004010798</t>
+          <t>3298283618399353069</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-04-20 16:54:22</t>
+          <t>2026-04-27 17:51:44</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园东方红</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>925</v>
+        <v>1778</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4502310699155008100</t>
+          <t>3298280018567005984</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-04-20 15:40:32</t>
+          <t>2026-04-27 16:59:44</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1113,27 +1106,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>加赠庄园蜜兰7g*1</t>
+          <t>岽顶蜜兰香7g*1 的差价金额</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>补差价链接：补拍金额=支付件数</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>928</v>
+        <v>1779</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4502307133133091420</t>
+          <t>5112440966305262918</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-04-20 14:04:50</t>
+          <t>2026-04-27 16:24:02</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1142,74 +1135,75 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>浓香芝兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>930</v>
+        <v>1781</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4502318798133010449</t>
+          <t>3298270874459005287</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-04-20 13:38:44</t>
+          <t>2026-04-27 16:20:24</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>100</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>加赠 羊脂玉茶具（含公道杯）*1
+加赠 庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>932</v>
+        <v>1784</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2701851060157004262</t>
+          <t>5112257331488027839</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-04-20 13:18:31</t>
+          <t>2026-04-27 16:08:19</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>100</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>清香鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>936</v>
+        <v>1787</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2701854840161029970</t>
+          <t>5112635148912150311</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-04-20 12:40:20</t>
+          <t>2026-04-27 15:42:06</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1218,22 +1212,22 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>939</v>
+        <v>1790</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4502309727120027322</t>
+          <t>3298853460841205462</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-04-20 12:35:07</t>
+          <t>2026-04-27 15:30:57</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1242,22 +1236,22 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>943</v>
+        <v>1792</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4502306269139047714</t>
+          <t>5112421022276007549</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-04-20 12:25:30</t>
+          <t>2026-04-27 15:00:09</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1266,216 +1260,596 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>945</v>
+        <v>1794</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2701853436146010798</t>
+          <t>3298701973709045853</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-04-20 11:30:50</t>
+          <t>2026-04-27 14:59:11</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>发顺丰空运</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>金香鸭屎+庄园蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>948</v>
+        <v>1797</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2701863157156010798</t>
+          <t>5112627336813002802</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-04-20 11:28:35</t>
+          <t>2026-04-27 14:58:22</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>加赠 羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>面值:面值B</t>
+          <t>老丛私房鸭屎香</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>949</v>
+        <v>1800</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2701851528152019357</t>
+          <t>3298680445420086984</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-04-20 10:23:03</t>
+          <t>2026-04-27 14:05:02</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>加赠：庄园蜜兰7g*2 咖啡色两罐装礼袋*2
-发顺丰</t>
+          <t>加赠 岽顶蜜兰香7g*1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>950</v>
+        <v>1804</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2701865065156070450</t>
+          <t>3298239878790028093</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-04-20 10:12:19</t>
+          <t>2026-04-27 13:31:49</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>加赠岽顶蜜兰香7g*1</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>952</v>
+        <v>1806</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2701866901147022371</t>
+          <t>5112343874960000927</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-04-20 09:47:34</t>
+          <t>2026-04-27 12:09:38</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>加赠 羊脂玉茶具（含公道杯）*1
+加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>954</v>
+        <v>1809</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2701862151138010492</t>
+          <t>5112539784161050427</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-04-20 09:19:55</t>
+          <t>2026-04-27 11:27:23</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>100</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>956</v>
+        <v>1811</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2701868629159005574</t>
+          <t>3298186346638108392</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-04-20 02:14:01</t>
+          <t>2026-04-27 11:09:53</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>加赠 清香桂花7g*1</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>金香鸭屎+庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>958</v>
+        <v>1814</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4502304252117005341</t>
+          <t>3298625545287027074</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-04-20 00:36:44</t>
+          <t>2026-04-27 10:54:10</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">加赠 庄园锯朵仔7g*1 </t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>1816</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3298143903828020998</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-04-27 10:45:02</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>面值:面值C</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>1817</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>3298185014420015983</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-04-27 10:37:35</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>加赠 清香桂花7g*1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>1819</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>5112139827952008302</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-04-27 10:32:40</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>加赠 羊脂玉茶具（含公道杯）*1
+加赠 庄园鸭屎7g*1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>十年陈窖藏蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>1822</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5112323714936135513</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-04-27 10:30:04</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>面值:面值F</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>1823</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>3298173674988045988</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-04-27 10:24:19</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>加赠 清香桂花7g*1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>悠山蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>1825</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>5112147963231005501</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-04-27 10:22:43</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>1828</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5112607573703076405</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-04-27 10:01:11</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>1831</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5112609409462006227</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-04-27 09:51:27</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>1833</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3298130547672029184</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-04-27 08:59:25</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>六大香型进阶版</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>1835</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>5112592237312003517</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-04-27 03:54:20</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>老丛私房鸭屎香</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>1837</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>3298601821307035958</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-04-27 03:36:21</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>清香桂花</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>1840</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>3298598761022035497</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-04-27 02:01:36</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>加赠 羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>庄园鸭屎+岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>1843</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5112504216092088537</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:26:29</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>取茶三件套*1 不需要发货
+加赠 岽顶蜜兰香7g*1
+加赠 庄园鸭屎7g*1
+加赠 羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>庄园锯朵仔</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>1846</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5112293366923039919</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:21:55</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>

--- a/old_send/db/new_df.xlsx
+++ b/old_send/db/new_df.xlsx
@@ -457,16 +457,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>1717</v>
+        <v>1628</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5112523442049028326</t>
+          <t>5119164758598126107</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-27 23:54:09</t>
+          <t>2026-06-08 23:57:31</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -481,16 +481,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1719</v>
+        <v>1630</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5112519986076166714</t>
+          <t>3307189332805005299</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-27 23:47:21</t>
+          <t>2026-06-08 23:55:05</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -498,27 +498,35 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>加赠 庄园锯朵仔7g*1</t>
+          <t>取茶三件套*2不发货！！！
+加赠：
+庄园蜜兰7g*1
+庄园东方红7g
+清香桂花7g*1
+庄园锯朵仔7g*1
+浓香芝兰7g*1
+金香鸭屎7g*1
+加赠老丛私房杏仁50g*1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1721</v>
+        <v>1633</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3298296507645009591</t>
+          <t>3306541695888050491</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-27 23:22:51</t>
+          <t>2026-06-08 23:51:47</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -526,27 +534,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>加赠 庄园锯朵仔7g*1</t>
+          <t>取茶三件套*1不发货</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>金香鸭屎+庄园蜜兰</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>1724</v>
+        <v>1636</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5112805429760005606</t>
+          <t>3306548571342004358</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-27 23:19:49</t>
+          <t>2026-06-08 23:45:46</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -555,50 +563,46 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>清香桂花</t>
+          <t>面值:面值F</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>1729</v>
+        <v>1637</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3298771237572157084</t>
+          <t>3307008973102088177</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-04-27 23:14:10</t>
+          <t>2026-06-08 23:21:54</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>1731</v>
+        <v>1639</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3298295283496021075</t>
+          <t>5119451965653002148</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-27 23:14:04</t>
+          <t>2026-06-08 23:02:36</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -607,46 +611,50 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>1733</v>
+        <v>1641</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5112726408581127828</t>
+          <t>3307193580339014097</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-04-27 22:59:20</t>
+          <t>2026-06-08 22:43:21</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>1735</v>
+        <v>1643</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5112514442110019507</t>
+          <t>3306999433780286455</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-27 22:45:23</t>
+          <t>2026-06-08 22:37:29</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -655,22 +663,22 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>1737</v>
+        <v>1645</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3298332686002021276</t>
+          <t>3306555410994097258</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-27 22:32:08</t>
+          <t>2026-06-08 22:33:27</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -679,74 +687,74 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>面值:面值C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>1740</v>
+        <v>1646</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3298291575757240996</t>
+          <t>3306542235581024670</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-27 22:26:34</t>
+          <t>2026-06-08 22:29:14</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>悠山蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>1742</v>
+        <v>1649</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5112509978019130530</t>
+          <t>5118948975893001117</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04-27 22:05:23</t>
+          <t>2026-06-08 22:13:33</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*2</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>老丛私房东方红</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>1744</v>
+        <v>1658</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3298326062360055354</t>
+          <t>3307005337404115184</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-27 21:41:36</t>
+          <t>2026-06-08 22:07:42</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -755,26 +763,26 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>悠山蜜兰</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>1746</v>
+        <v>1662</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5112505190676074648</t>
+          <t>5119364520757001329</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-04-27 21:27:37</t>
+          <t>2026-06-08 21:57:03</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
@@ -785,16 +793,16 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>1750</v>
+        <v>1665</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5112711648883129839</t>
+          <t>5118951675435039632</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-27 21:26:10</t>
+          <t>2026-06-08 21:44:26</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -803,22 +811,22 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>面值:面值F</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>1751</v>
+        <v>1667</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5112797257142002615</t>
+          <t>5119164758393027824</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04-27 21:25:09</t>
+          <t>2026-06-08 21:18:41</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -833,16 +841,16 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>1754</v>
+        <v>1668</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5112709704142072014</t>
+          <t>3306555878977056464</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-04-27 21:05:49</t>
+          <t>2026-06-08 21:11:17</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -851,22 +859,22 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>1756</v>
+        <v>1671</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3298909656231001962</t>
+          <t>3307183212751031565</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-04-27 20:44:28</t>
+          <t>2026-06-08 21:07:27</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -875,22 +883,22 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>悠山蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>1758</v>
+        <v>1673</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3298907496459088759</t>
+          <t>3306997705338003673</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-04-27 20:43:47</t>
+          <t>2026-06-08 20:50:22</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -899,46 +907,50 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>十年陈窖藏蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>1761</v>
+        <v>1675</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3298304966989028575</t>
+          <t>5118953439083016745</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-04-27 19:59:54</t>
+          <t>2026-06-08 20:25:15</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>1763</v>
+        <v>1678</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5112687708374004315</t>
+          <t>5119447969054021341</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-27 19:30:11</t>
+          <t>2026-06-08 20:24:03</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -946,27 +958,33 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+          <t>按照备注发货，实际发货：
+岽顶蜜兰50g*10罐
+岽顶蜜兰7g*1
+清香桂花7g*1
+庄园鸭屎7g*1
+羊脂玉茶具（含公道杯）*1
+取茶三件套不发货！！！</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>1766</v>
+        <v>1681</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3298297982545013493</t>
+          <t>3306558254853009869</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-04-27 19:16:37</t>
+          <t>2026-06-08 20:20:17</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -975,22 +993,22 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>1768</v>
+        <v>1683</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5112293943305001921</t>
+          <t>3306983341996069265</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-04-27 19:02:50</t>
+          <t>2026-06-08 20:10:55</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -998,27 +1016,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>加赠庄园蜜兰7g*1</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>老丛私房蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>1770</v>
+        <v>1685</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3298881036207024386</t>
+          <t>5118941667523167142</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-04-27 18:16:54</t>
+          <t>2026-06-08 19:02:02</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1027,22 +1045,22 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>1773</v>
+        <v>1688</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3298293410900024386</t>
+          <t>5118945087153076317</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-04-27 17:55:26</t>
+          <t>2026-06-08 18:33:17</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1050,11 +1068,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>加赠 老丛私房杏仁50g*2
- 加赠 羊脂玉茶具（含公道杯）*1
-加赠 岽顶蜜兰香7g*1
-加赠 庄园锯朵仔7g*1
-加赠 十年陈鸭屎香7g*1</t>
+          <t>加赠清香桂花7g*1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1065,68 +1079,68 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>1776</v>
+        <v>1692</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3298283618399353069</t>
+          <t>3306516423310038550</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-04-27 17:51:44</t>
+          <t>2026-06-08 18:08:31</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>庄园东方红</t>
+          <t>老丛私房东方红</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>1778</v>
+        <v>1695</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3298280018567005984</t>
+          <t>3306547058328026469</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-04-27 16:59:44</t>
+          <t>2026-06-08 17:48:22</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>岽顶蜜兰香7g*1 的差价金额</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>补差价链接：补拍金额=支付件数</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>1779</v>
+        <v>1697</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5112440966305262918</t>
+          <t>3306523299386023194</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-04-27 16:24:02</t>
+          <t>2026-06-08 17:45:54</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1135,75 +1149,74 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>1781</v>
+        <v>1700</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3298270874459005287</t>
+          <t>5118944079292002201</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-04-27 16:20:24</t>
+          <t>2026-06-08 17:03:00</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>加赠 羊脂玉茶具（含公道杯）*1
-加赠 庄园鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>1784</v>
+        <v>1702</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5112257331488027839</t>
+          <t>5119442425782013041</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-04-27 16:08:19</t>
+          <t>2026-06-08 16:45:58</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>十年陈窖藏蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>1787</v>
+        <v>1705</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5112635148912150311</t>
+          <t>5119358508151014214</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-04-27 15:42:06</t>
+          <t>2026-06-08 16:00:59</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1212,46 +1225,51 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>1790</v>
+        <v>1707</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3298853460841205462</t>
+          <t>3307139652492016785</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-04-27 15:30:57</t>
+          <t>2026-06-08 15:26:09</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>加赠 老丛私房杏仁50g*1
+加赠 羊脂玉茶具（含公道杯）*2</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>老丛私房宋种</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>1792</v>
+        <v>1720</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5112421022276007549</t>
+          <t>5118927987125008521</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-04-27 15:00:09</t>
+          <t>2026-06-08 15:19:51</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1260,22 +1278,22 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>1794</v>
+        <v>1722</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3298701973709045853</t>
+          <t>3306514262869016785</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-04-27 14:59:11</t>
+          <t>2026-06-08 15:18:36</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1284,155 +1302,154 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>面值:面值C</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>1797</v>
+        <v>1723</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5112627336813002802</t>
+          <t>3306947413154001390</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-04-27 14:58:22</t>
+          <t>2026-06-08 14:24:38</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>加赠 羊脂玉茶具（含公道杯）*1</t>
+          <t xml:space="preserve">加赠 庄园锯朵仔7g*1 </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>老丛私房鸭屎香</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>1800</v>
+        <v>1725</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3298680445420086984</t>
+          <t>5119431517100034934</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-04-27 14:05:02</t>
+          <t>2026-06-08 14:22:11</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>加赠 岽顶蜜兰香7g*1</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>清香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>1804</v>
+        <v>1727</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3298239878790028093</t>
+          <t>3307129968876003586</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-04-27 13:31:49</t>
+          <t>2026-06-08 14:16:19</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>1806</v>
+        <v>1729</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5112343874960000927</t>
+          <t>3306918613190106184</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-04-27 12:09:38</t>
+          <t>2026-06-08 14:05:04</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>加赠 羊脂玉茶具（含公道杯）*1
-加赠 岽顶蜜兰香7g*1</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>1809</v>
+        <v>1733</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5112539784161050427</t>
+          <t>3306470883576035292</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-04-27 11:27:23</t>
+          <t>2026-06-08 14:01:43</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>1811</v>
+        <v>1743</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3298186346638108392</t>
+          <t>3306497990137008377</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-04-27 11:09:53</t>
+          <t>2026-06-08 13:49:10</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1440,79 +1457,79 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>加赠 清香桂花7g*1</t>
+          <t xml:space="preserve">加赠 庄园锯朵仔7g*1 </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>金香鸭屎+庄园蜜兰</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>1814</v>
+        <v>1745</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3298625545287027074</t>
+          <t>5118916647064081935</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-04-27 10:54:10</t>
+          <t>2026-06-08 12:46:42</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">加赠 庄园锯朵仔7g*1 </t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>1816</v>
+        <v>1751</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3298143903828020998</t>
+          <t>5118909987914024345</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-04-27 10:45:02</t>
+          <t>2026-06-08 11:25:07</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>加赠 清香桂花7g*1</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>面值:面值C</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>1817</v>
+        <v>1753</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3298185014420015983</t>
+          <t>5119129298145003620</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-04-27 10:37:35</t>
+          <t>2026-06-08 10:04:02</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1520,27 +1537,27 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>加赠 清香桂花7g*1</t>
+          <t>加赠 金香鸭屎7g*1</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>1819</v>
+        <v>1755</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5112139827952008302</t>
+          <t>3307083636610022172</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-04-27 10:32:40</t>
+          <t>2026-06-08 09:50:45</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1548,28 +1565,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>加赠 羊脂玉茶具（含公道杯）*1
-加赠 庄园鸭屎7g*1</t>
+          <t>加赠庄园鸭屎7g*1</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>十年陈窖藏蜜兰香</t>
+          <t>悠山蜜兰</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>1822</v>
+        <v>1757</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5112323714936135513</t>
+          <t>3307088748668022890</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-04-27 10:30:04</t>
+          <t>2026-06-08 09:23:16</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1578,22 +1594,22 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>面值:面值F</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>1823</v>
+        <v>1759</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3298173674988045988</t>
+          <t>5119415425822003715</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-04-27 10:24:19</t>
+          <t>2026-06-08 09:12:01</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1601,27 +1617,28 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>加赠 清香桂花7g*1</t>
+          <t>加赠 庄园东方红7g*1
+加赠 清香桂花7g*1</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>悠山蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>1825</v>
+        <v>1765</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5112147963231005501</t>
+          <t>5119329492602000120</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-04-27 10:22:43</t>
+          <t>2026-06-08 07:43:27</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1629,55 +1646,51 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>加赠 岽顶蜜兰香7g*1</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>老丛私房宋种</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>1828</v>
+        <v>1767</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5112607573703076405</t>
+          <t>3306458606354024793</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-04-27 10:01:11</t>
+          <t>2026-06-08 06:46:49</t>
         </is>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>加赠 岽顶蜜兰香7g*1</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>1831</v>
+        <v>1770</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5112609409462006227</t>
+          <t>5118915027172001735</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-04-27 09:51:27</t>
+          <t>2026-06-08 04:37:47</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1685,27 +1698,27 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>加赠 岽顶蜜兰香7g*1</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>1833</v>
+        <v>1773</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3298130547672029184</t>
+          <t>5119126022773001735</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-04-27 08:59:25</t>
+          <t>2026-06-08 04:35:25</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1714,22 +1727,22 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>1835</v>
+        <v>1776</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5112592237312003517</t>
+          <t>5119129658095001735</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-04-27 03:54:20</t>
+          <t>2026-06-08 04:20:19</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1738,78 +1751,70 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>老丛私房鸭屎香</t>
+          <t>面值:面值C</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>1837</v>
+        <v>1777</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3298601821307035958</t>
+          <t>5118910203855006223</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-04-27 03:36:21</t>
+          <t>2026-06-08 03:20:53</t>
         </is>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>加赠 岽顶蜜兰香7g*1</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>清香桂花</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>1840</v>
+        <v>1779</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3298598761022035497</t>
+          <t>3306885457517054794</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-04-27 02:01:36</t>
+          <t>2026-06-08 02:05:22</t>
         </is>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>加赠 羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>庄园鸭屎+岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>1843</v>
+        <v>1781</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5112504216092088537</t>
+          <t>5119419673016035633</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-04-27 00:26:29</t>
+          <t>2026-06-08 00:44:45</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1817,30 +1822,27 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>取茶三件套*1 不需要发货
-加赠 岽顶蜜兰香7g*1
-加赠 庄园鸭屎7g*1
-加赠 羊脂玉茶具（含公道杯）*1</t>
+          <t>加赠老丛私房杏仁50g*1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>1846</v>
+        <v>1787</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5112293366923039919</t>
+          <t>3306887293914006655</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-04-27 00:21:55</t>
+          <t>2026-06-08 00:38:19</t>
         </is>
       </c>
       <c r="D55" t="n">

--- a/old_send/db/new_df.xlsx
+++ b/old_send/db/new_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,16 +457,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>1628</v>
+        <v>1859</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5119164758598126107</t>
+          <t>5119872339312025614</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-08 23:57:31</t>
+          <t>2026-06-15 23:55:33</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -475,22 +475,22 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1630</v>
+        <v>1861</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3307189332805005299</t>
+          <t>5119874643156022543</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:55:05</t>
+          <t>2026-06-15 23:48:00</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -498,87 +498,80 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>取茶三件套*2不发货！！！
-加赠：
-庄园蜜兰7g*1
-庄园东方红7g
-清香桂花7g*1
-庄园锯朵仔7g*1
-浓香芝兰7g*1
-金香鸭屎7g*1
-加赠老丛私房杏仁50g*1</t>
+          <t>和订单号4502221849125022543累计满赠
+加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>老丛私房鸭屎香</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1633</v>
+        <v>1863</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3306541695888050491</t>
+          <t>3307938999206018695</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-08 23:51:47</t>
+          <t>2026-06-15 23:31:22</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>取茶三件套*1不发货</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>1636</v>
+        <v>1865</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3306548571342004358</t>
+          <t>3308396089079073155</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-08 23:45:46</t>
+          <t>2026-06-15 23:27:57</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>面值:面值F</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>1637</v>
+        <v>1868</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3307008973102088177</t>
+          <t>3307956278828015993</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-08 23:21:54</t>
+          <t>2026-06-15 23:14:52</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -587,46 +580,50 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>浓香芝兰</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>1639</v>
+        <v>1870</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5119451965653002148</t>
+          <t>3308399221211019251</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-08 23:02:36</t>
+          <t>2026-06-15 23:11:54</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>老丛私房姜花香</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>1641</v>
+        <v>1874</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3307193580339014097</t>
+          <t>3307930143908016596</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-08 22:43:21</t>
+          <t>2026-06-15 23:11:08</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -639,22 +636,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>1643</v>
+        <v>1876</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3306999433780286455</t>
+          <t>5120297856204075521</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-08 22:37:29</t>
+          <t>2026-06-15 23:08:00</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -663,46 +660,50 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>1645</v>
+        <v>1878</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3306555410994097258</t>
+          <t>5119870647719000744</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-08 22:33:27</t>
+          <t>2026-06-15 23:07:57</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>面值:面值C</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>1646</v>
+        <v>1880</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3306542235581024670</t>
+          <t>3308577060083087983</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-08 22:29:14</t>
+          <t>2026-06-15 23:07:16</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -711,22 +712,22 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>金香鸭屎+庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>1649</v>
+        <v>1883</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5118948975893001117</t>
+          <t>5119868883673015931</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-08 22:13:33</t>
+          <t>2026-06-15 23:05:31</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -734,51 +735,55 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>加赠老丛私房杏仁50g*2</t>
+          <t>加赠庄园鸭屎7g*1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>老丛私房东方红</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>1658</v>
+        <v>1886</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3307005337404115184</t>
+          <t>5120378353085031445</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-08 22:07:42</t>
+          <t>2026-06-15 22:53:32</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>1662</v>
+        <v>1889</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5119364520757001329</t>
+          <t>5120082758572025216</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-08 21:57:03</t>
+          <t>2026-06-15 22:51:45</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -787,22 +792,22 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>1665</v>
+        <v>1891</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5118951675435039632</t>
+          <t>5120082434605144808</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-08 21:44:26</t>
+          <t>2026-06-15 22:36:55</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -811,22 +816,22 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>悠山蜜兰</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>1667</v>
+        <v>1893</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5119164758393027824</t>
+          <t>5120085890208085912</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-08 21:18:41</t>
+          <t>2026-06-15 22:35:21</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -841,40 +846,44 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>1668</v>
+        <v>1895</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3306555878977056464</t>
+          <t>5120373493849032743</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-08 21:11:17</t>
+          <t>2026-06-15 22:35:16</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>加赠清香桂花7g*1</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>1671</v>
+        <v>1899</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3307183212751031565</t>
+          <t>5119865427950032341</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-08 21:07:27</t>
+          <t>2026-06-15 22:31:54</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -883,46 +892,46 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>1673</v>
+        <v>1901</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3306997705338003673</t>
+          <t>5120292996680052804</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-08 20:50:22</t>
+          <t>2026-06-15 22:28:50</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>1675</v>
+        <v>1905</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5118953439083016745</t>
+          <t>5120084234381025635</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-08 20:25:15</t>
+          <t>2026-06-15 22:21:28</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -930,61 +939,51 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+          <t>加赠老丛私房杏仁50g*1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>1678</v>
+        <v>1909</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5119447969054021341</t>
+          <t>5120082686536035243</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06-08 20:24:03</t>
+          <t>2026-06-15 22:21:08</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>按照备注发货，实际发货：
-岽顶蜜兰50g*10罐
-岽顶蜜兰7g*1
-清香桂花7g*1
-庄园鸭屎7g*1
-羊脂玉茶具（含公道杯）*1
-取茶三件套不发货！！！</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>1681</v>
+        <v>1911</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3306558254853009869</t>
+          <t>5120292060718000538</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-06-08 20:20:17</t>
+          <t>2026-06-15 22:12:19</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -993,50 +992,46 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>1683</v>
+        <v>1913</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3306983341996069265</t>
+          <t>3307930827254025070</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-06-08 20:10:55</t>
+          <t>2026-06-15 21:50:22</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>老丛私房蜜兰香</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>1685</v>
+        <v>1915</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5118941667523167142</t>
+          <t>5120293032529035414</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-06-08 19:02:02</t>
+          <t>2026-06-15 21:46:20</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1045,102 +1040,98 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>1688</v>
+        <v>1918</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5118945087153076317</t>
+          <t>5120376265291021520</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-06-08 18:33:17</t>
+          <t>2026-06-15 21:33:39</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>加赠清香桂花7g*1</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>1692</v>
+        <v>1920</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3306516423310038550</t>
+          <t>3308387305485034767</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-06-08 18:08:31</t>
+          <t>2026-06-15 21:26:51</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>加赠老丛私房杏仁50g*1</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>老丛私房东方红</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>1695</v>
+        <v>1924</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3306547058328026469</t>
+          <t>3307950806206097959</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-06-08 17:48:22</t>
+          <t>2026-06-15 21:22:05</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>老丛私房宋种</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>1697</v>
+        <v>1926</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3306523299386023194</t>
+          <t>5119870287453023111</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-06-08 17:45:54</t>
+          <t>2026-06-15 21:18:34</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1155,68 +1146,68 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>1700</v>
+        <v>1928</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5118944079292002201</t>
+          <t>3308386729934009573</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-06-08 17:03:00</t>
+          <t>2026-06-15 21:18:17</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>清香桂花</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>1702</v>
+        <v>1931</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5119442425782013041</t>
+          <t>3307914447961160383</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-06-08 16:45:58</t>
+          <t>2026-06-15 21:18:00</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>十年陈窖藏蜜兰香</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>1705</v>
+        <v>1934</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5119358508151014214</t>
+          <t>5120290908033023315</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-06-08 16:00:59</t>
+          <t>2026-06-15 21:16:23</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1231,16 +1222,16 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>1707</v>
+        <v>1936</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3307139652492016785</t>
+          <t>5119870287196005113</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-06-08 15:26:09</t>
+          <t>2026-06-15 21:08:34</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1248,28 +1239,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>加赠 老丛私房杏仁50g*1
-加赠 羊脂玉茶具（含公道杯）*2</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>老丛私房宋种</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>1720</v>
+        <v>1944</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5118927987125008521</t>
+          <t>3307945334998001381</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-06-08 15:19:51</t>
+          <t>2026-06-15 21:08:32</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1278,46 +1268,50 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>1722</v>
+        <v>1946</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3306514262869016785</t>
+          <t>3308566584275003390</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-06-08 15:18:36</t>
+          <t>2026-06-15 21:07:50</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>面值:面值C</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>1723</v>
+        <v>1949</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3306947413154001390</t>
+          <t>5120371009637153825</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-06-08 14:24:38</t>
+          <t>2026-06-15 21:07:48</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1325,27 +1319,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">加赠 庄园锯朵仔7g*1 </t>
+          <t>加赠庄园蜜兰7g*1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>1725</v>
+        <v>1952</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5119431517100034934</t>
+          <t>5120074586567173514</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-06-08 14:22:11</t>
+          <t>2026-06-15 21:05:27</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1354,50 +1348,46 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>清香鸭屎</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>1727</v>
+        <v>1955</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3307129968876003586</t>
+          <t>3307948250542005394</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-06-08 14:16:19</t>
+          <t>2026-06-15 20:58:04</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>1729</v>
+        <v>1957</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3306918613190106184</t>
+          <t>5120292744262000704</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-06-08 14:05:04</t>
+          <t>2026-06-15 20:57:12</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1406,140 +1396,128 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>1733</v>
+        <v>1960</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3306470883576035292</t>
+          <t>5120287956385005113</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-06-08 14:01:43</t>
+          <t>2026-06-15 20:52:04</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>待 发货</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>面值:面值C</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>1743</v>
+        <v>1961</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3306497990137008377</t>
+          <t>5120287488750122033</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-06-08 13:49:10</t>
+          <t>2026-06-15 20:51:37</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">加赠 庄园锯朵仔7g*1 </t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>1745</v>
+        <v>1964</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5118916647064081935</t>
+          <t>3308375462000121671</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-06-08 12:46:42</t>
+          <t>2026-06-15 20:45:22</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>老丛私房宋种</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>1751</v>
+        <v>1969</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5118909987914024345</t>
+          <t>3308384137899049651</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-06-08 11:25:07</t>
+          <t>2026-06-15 20:42:34</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>加赠 清香桂花7g*1</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>面值:面值B</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>1753</v>
+        <v>1970</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5119129298145003620</t>
+          <t>3307944866128014356</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-06-08 10:04:02</t>
+          <t>2026-06-15 20:28:38</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>加赠 金香鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -1548,44 +1526,40 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>1755</v>
+        <v>1973</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3307083636610022172</t>
+          <t>5120079086455046143</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-06-08 09:50:45</t>
+          <t>2026-06-15 20:25:08</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>悠山蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>1757</v>
+        <v>1975</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3307088748668022890</t>
+          <t>3307936730380197359</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-06-08 09:23:16</t>
+          <t>2026-06-15 20:19:55</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1594,51 +1568,46 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>1759</v>
+        <v>1978</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5119415425822003715</t>
+          <t>5120286228272029228</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-06-08 09:12:01</t>
+          <t>2026-06-15 20:17:40</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>加赠 庄园东方红7g*1
-加赠 清香桂花7g*1</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>1765</v>
+        <v>1981</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5119329492602000120</t>
+          <t>5120371945498164906</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-06-08 07:43:27</t>
+          <t>2026-06-15 20:13:22</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1646,79 +1615,80 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+          <t>加赠金香鸭屎7g*1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>老丛私房宋种</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>1767</v>
+        <v>1983</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3306458606354024793</t>
+          <t>3307920747006006694</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-06-08 06:46:49</t>
+          <t>2026-06-15 20:13:06</t>
         </is>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>加赠凤凰快客杯*1加赠六大组合品鉴装7g*6
+取茶三件套*2不要发货！！！</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>1770</v>
+        <v>1989</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5118915027172001735</t>
+          <t>3308383525463006694</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-06-08 04:37:47</t>
+          <t>2026-06-15 20:11:40</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>面值:面值C</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>1773</v>
+        <v>1990</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5119126022773001735</t>
+          <t>3308381077963024183</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-06-08 04:35:25</t>
+          <t>2026-06-15 20:08:20</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1727,46 +1697,50 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>1776</v>
+        <v>1993</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5119129658095001735</t>
+          <t>5120289144186005908</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-06-08 04:20:19</t>
+          <t>2026-06-15 20:01:53</t>
         </is>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>面值:面值C</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>1777</v>
+        <v>1996</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5118910203855006223</t>
+          <t>5120369389553030103</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-06-08 03:20:53</t>
+          <t>2026-06-15 19:59:35</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1775,22 +1749,22 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>1779</v>
+        <v>1998</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3306885457517054794</t>
+          <t>3307914375512123853</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-06-08 02:05:22</t>
+          <t>2026-06-15 19:58:39</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1805,16 +1779,16 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>1781</v>
+        <v>2004</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5119419673016035633</t>
+          <t>3307925462397053892</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-06-08 00:44:45</t>
+          <t>2026-06-15 19:40:24</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1822,34 +1796,1188 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>加赠老丛私房杏仁50g*1</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1加赠庄园鸭屎7g*1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>1787</v>
+        <v>2007</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3306887293914006655</t>
+          <t>5120289036212006725</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-06-08 00:38:19</t>
+          <t>2026-06-15 19:29:29</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
+        <is>
+          <t>老丛私房鸭屎香</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>3307883703258105297</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-06-15 19:24:24</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5120288460083005829</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-06-15 19:23:01</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>面值:面值C</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>3307933886202010382</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-06-15 19:13:24</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>老丛私房八仙</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5119864419138001417</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-06-15 19:07:29</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>3307911819541006267</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-06-15 19:05:20</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>3308377405516000560</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-06-15 18:53:56</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5120362081653015907</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-06-15 18:26:58</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>3308548476691018284</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-06-15 18:23:27</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>3308553912101054294</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-06-15 18:23:01</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5119846059981017718</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-06-15 17:00:15</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>加赠 老丛私房杏仁50g*1</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5120068502548008536</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:56:33</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>面值:面值C</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>3307892091780006876</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:55:19</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>浓香芝兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5120070122477003636</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:48:14</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>3307875747778000596</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:29:43</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>2043</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>3308314945804044755</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:22:18</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>2046</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5119852071660011743</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:20:21</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>2049</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>5119837671368036936</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:55:15</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>加赠清香桂花7g*1</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>2057</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>3308323441607013686</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:46:24</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>2059</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>3308306053332008650</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:43:46</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>2061</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>3307863399182005254</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:41:03</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1加赠清香桂花7g*1加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>2064</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>5119827051103006307</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:39:54</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>2066</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5120248356751013041</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:38:37</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>2069</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3308305117309012386</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:28:59</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1 加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>2072</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>3308480760425120375</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:19:10</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>2074</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>5119814091306022223</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:10:13</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>面值:面值C</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>2075</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5119944734411096944</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:02:35</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>2079</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5120023574640006617</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:48:41</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>2085</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5120207640348220731</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:23:34</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>2089</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5120149680435013148</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:27:28</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>2092</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5120175960773032604</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:58:49</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>加赠 咖啡色两罐装礼袋*1</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>庄园锯朵仔</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>2096</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>3308390580314115487</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:54:04</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>加赠岽顶蜜兰香7g*1加赠清香桂花7g*1</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>2099</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>3307760547433008782</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:52:13</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>2102</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>3308391336455022279</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:48:44</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>3308386008687009288</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:47:07</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>按备注发货！！ 实际发：
+庄园蜜兰7g*73
+（需要用6袋白色盒子装）</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>2108</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>5120172108715055615</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:47:00</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>2110</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>5119938650820015233</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:13:07</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>2112</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5120151336178008527</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:26:28</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>100</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>2115</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5119721319531008527</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:23:39</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1元预定赠品兑换券</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>2116</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>5119928066791001727</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-06-15 10:41:09</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>2119</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5120223085971023840</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-06-15 10:24:09</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>2122</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5120137044527019006</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-06-15 09:51:11</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>清香桂花</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>2125</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>3308360664128112093</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-06-15 09:28:55</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>2128</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>3308154457573023867</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-06-15 07:33:03</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>庄园东方红</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>2130</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>5120107776791180111</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-06-15 01:16:01</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>2133</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>3308336400255033772</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-06-15 01:12:18</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>100</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
         <is>
           <t>金香鸭屎</t>
         </is>
